--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,112 +12030,112 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ59" t="n">
         <v>0</v>
@@ -12144,25 +12144,25 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI59" s="3" t="n">
         <v>46110.5</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,112 +12621,112 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ62" t="n">
         <v>0</v>
@@ -12735,25 +12735,25 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
         <v>46110.5</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,112 +12030,112 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
         <v>0</v>
@@ -12144,25 +12144,25 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
         <v>46110.5</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8283,7 +8283,7 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,112 +13015,112 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK64" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL64" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM64" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN64" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO64" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP64" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV64" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX64" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY64" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ64" t="n">
         <v>0</v>
@@ -13129,25 +13129,25 @@
         <v>0</v>
       </c>
       <c r="BB64" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC64" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD64" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE64" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF64" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG64" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI64" s="3" t="n">
         <v>46110.5</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,83 +8480,83 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,16 +8598,16 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,112 +13015,112 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK64" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL64" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM64" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN64" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO64" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT64" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU64" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV64" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ64" t="n">
         <v>0</v>
@@ -13129,25 +13129,25 @@
         <v>0</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC64" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD64" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
         <v>46110.5</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,16 +8401,16 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,83 +8480,83 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,16 +8598,16 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,112 +12227,112 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S60" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U60" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V60" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB60" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC60" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG60" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI60" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK60" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL60" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM60" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN60" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ60" t="n">
         <v>0</v>
@@ -12341,25 +12341,25 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI60" s="3" t="n">
         <v>46110.5</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,16 +8401,16 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,112 +12227,112 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI60" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK60" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL60" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM60" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN60" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO60" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS60" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT60" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV60" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW60" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX60" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY60" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ60" t="n">
         <v>0</v>
@@ -12341,25 +12341,25 @@
         <v>0</v>
       </c>
       <c r="BB60" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC60" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD60" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE60" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF60" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG60" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
         <v>46110.5</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,16 +8598,16 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,112 +12424,112 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP61" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY61" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ61" t="n">
         <v>0</v>
@@ -12538,25 +12538,25 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG61" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI61" s="3" t="n">
         <v>46110.5</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,16 +8598,16 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,112 +12030,112 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S59" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T59" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U59" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V59" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC59" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD59" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG59" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH59" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL59" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM59" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP59" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT59" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU59" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV59" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW59" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX59" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY59" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ59" t="n">
         <v>0</v>
@@ -12144,25 +12144,25 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC59" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD59" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE59" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF59" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI59" s="3" t="n">
         <v>46110.5</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,112 +12424,112 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ61" t="n">
         <v>0</v>
@@ -12538,25 +12538,25 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC61" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD61" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
         <v>46110.5</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,112 +12030,112 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T59" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U59" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V59" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC59" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH59" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI59" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL59" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM59" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN59" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO59" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU59" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV59" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW59" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ59" t="n">
         <v>0</v>
@@ -12144,25 +12144,25 @@
         <v>0</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC59" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD59" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI59" s="3" t="n">
         <v>46110.5</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12617,17 +12617,17 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="R85" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R87" t="n">
-        <v>2.73</v>
+        <v>3.44</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.76</v>
+        <v>4.69</v>
       </c>
       <c r="R88" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>8.550000000000001</v>
+        <v>2.31</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.25</v>
+        <v>2.67</v>
       </c>
       <c r="R89" t="n">
-        <v>1.26</v>
+        <v>3.42</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.69</v>
+        <v>5.25</v>
       </c>
       <c r="R90" t="n">
-        <v>5.4</v>
+        <v>1.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -12617,7 +12617,7 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P62" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R88" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.67</v>
+        <v>4.69</v>
       </c>
       <c r="R89" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,16 +8795,16 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.76</v>
+        <v>4.69</v>
       </c>
       <c r="R87" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.31</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.67</v>
+        <v>5.25</v>
       </c>
       <c r="R88" t="n">
-        <v>3.42</v>
+        <v>1.26</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="R89" t="n">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>8.550000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.25</v>
+        <v>2.78</v>
       </c>
       <c r="R90" t="n">
-        <v>1.26</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R91" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>4.69</v>
       </c>
       <c r="R86" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9859,7 +9859,7 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P48" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R85" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.67</v>
+        <v>4.69</v>
       </c>
       <c r="R87" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>8.550000000000001</v>
+        <v>2.24</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.25</v>
+        <v>2.76</v>
       </c>
       <c r="R88" t="n">
-        <v>1.26</v>
+        <v>3.44</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R89" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R92" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.47</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.78</v>
+        <v>5.25</v>
       </c>
       <c r="R85" t="n">
-        <v>2.99</v>
+        <v>1.26</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.31</v>
+        <v>1.56</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>4.69</v>
       </c>
       <c r="R86" t="n">
-        <v>3.42</v>
+        <v>5.4</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>8.550000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.25</v>
+        <v>2.78</v>
       </c>
       <c r="R89" t="n">
-        <v>1.26</v>
+        <v>2.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R92" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R93" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P104" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,16 +8992,16 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,112 +11242,112 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.67</v>
+        <v>3.92</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>4.88</v>
+        <v>1.81</v>
       </c>
       <c r="S55" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG55" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL55" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN55" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT55" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX55" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY55" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ55" t="n">
         <v>0</v>
@@ -11356,25 +11356,25 @@
         <v>0</v>
       </c>
       <c r="BB55" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC55" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD55" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE55" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF55" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG55" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
         <v>46110.5</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,112 +12424,112 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP61" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS61" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU61" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW61" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX61" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY61" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ61" t="n">
         <v>0</v>
@@ -12538,25 +12538,25 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG61" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH61" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI61" s="3" t="n">
         <v>46110.5</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="R87" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R88" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="R89" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R92" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R93" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>4.47</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,16 +8992,16 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R48" t="n">
-        <v>6.81</v>
+        <v>2.47</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,16 +9977,16 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>3.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>1.81</v>
+        <v>3.6</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,112 +12424,112 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.67</v>
+        <v>3.92</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>4.88</v>
+        <v>1.81</v>
       </c>
       <c r="S61" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U61" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V61" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD61" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AG61" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI61" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL61" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM61" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN61" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS61" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV61" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ61" t="n">
         <v>0</v>
@@ -12538,25 +12538,25 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC61" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD61" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF61" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG61" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH61" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
         <v>46110.5</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,116 +12814,116 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO63" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP63" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX63" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ63" t="n">
         <v>0</v>
@@ -12932,25 +12932,25 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI63" s="3" t="n">
         <v>46110.5</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>8.550000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="Q85" t="n">
-        <v>5.25</v>
+        <v>2.78</v>
       </c>
       <c r="R85" t="n">
-        <v>1.26</v>
+        <v>2.99</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="R86" t="n">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.31</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.67</v>
+        <v>5.25</v>
       </c>
       <c r="R89" t="n">
-        <v>3.42</v>
+        <v>1.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.74</v>
+        <v>4.69</v>
       </c>
       <c r="R90" t="n">
-        <v>2.73</v>
+        <v>5.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R91" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R92" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R93" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21285,7 +21285,7 @@
       </c>
       <c r="O106" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P106" t="n">
@@ -21482,7 +21482,7 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>16.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>3.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>4.47</v>
+        <v>2.05</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,116 +12814,116 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U63" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V63" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD63" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN63" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO63" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP63" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT63" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU63" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV63" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX63" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY63" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ63" t="n">
         <v>0</v>
@@ -12932,25 +12932,25 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC63" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE63" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF63" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG63" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH63" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
         <v>46110.5</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16403,10 +16403,10 @@
         <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R85" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R86" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="R87" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R88" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>8.550000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.25</v>
+        <v>4.69</v>
       </c>
       <c r="R89" t="n">
-        <v>1.26</v>
+        <v>5.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R90" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R91" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R92" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R93" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G107" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI107"/>
+  <dimension ref="A1:BI110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.47</v>
+        <v>6.81</v>
       </c>
       <c r="S48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,16 +9977,16 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>4.88</v>
+        <v>3.6</v>
       </c>
       <c r="S57" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,112 +12621,112 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ62" t="n">
         <v>0</v>
@@ -12735,25 +12735,25 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI62" s="3" t="n">
         <v>46110.5</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46110.52083333334</v>
+        <v>46110.5</v>
       </c>
     </row>
     <row r="67">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46110.54166666666</v>
+        <v>46110.52083333334</v>
       </c>
     </row>
     <row r="73">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46110.5625</v>
+        <v>46110.54166666666</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15966,137 +15966,137 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.72</v>
+        <v>2.83</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R79" t="n">
-        <v>4.2</v>
+        <v>2.53</v>
       </c>
       <c r="S79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U79" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V79" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W79" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD79" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.03</v>
+        <v>1.81</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL79" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN79" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO79" t="n">
         <v>0</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR79" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS79" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT79" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV79" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX79" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA79" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB79" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE79" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF79" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46110.58333333334</v>
+        <v>46110.5625</v>
       </c>
     </row>
     <row r="80">
@@ -16114,27 +16114,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,137 +16163,137 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46110.625</v>
+        <v>46110.58333333334</v>
       </c>
     </row>
     <row r="81">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46110.64583333334</v>
+        <v>46110.58333333334</v>
       </c>
     </row>
     <row r="82">
@@ -16508,27 +16508,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46110.64583333334</v>
+        <v>46110.625</v>
       </c>
     </row>
     <row r="83">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17099,27 +17099,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46110.66666666666</v>
+        <v>46110.64583333334</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46110.66666666666</v>
+        <v>46110.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.74</v>
+        <v>5.25</v>
       </c>
       <c r="R87" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17739,17 +17739,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="R90" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18281,7 +18281,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>3.13</v>
+        <v>2.31</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="R91" t="n">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46110.70833333334</v>
+        <v>46110.66666666666</v>
       </c>
     </row>
     <row r="92">
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46110.70833333334</v>
+        <v>46110.66666666666</v>
       </c>
     </row>
     <row r="93">
@@ -18675,7 +18675,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.22</v>
+        <v>2.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="R93" t="n">
-        <v>3.48</v>
+        <v>2.73</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46110.70833333334</v>
+        <v>46110.66666666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,27 +18872,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46110.72916666666</v>
+        <v>46110.66666666666</v>
       </c>
     </row>
     <row r="95">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46110.72916666666</v>
+        <v>46110.70833333334</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46110.72916666666</v>
+        <v>46110.70833333334</v>
       </c>
     </row>
     <row r="97">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.85</v>
+        <v>3.13</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="R97" t="n">
-        <v>5.04</v>
+        <v>2.37</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46110.72916666666</v>
+        <v>46110.70833333334</v>
       </c>
     </row>
     <row r="98">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46110.75</v>
+        <v>46110.72916666666</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46110.75</v>
+        <v>46110.72916666666</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46110.77083333334</v>
+        <v>46110.72916666666</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46110.83333333334</v>
+        <v>46110.72916666666</v>
       </c>
     </row>
     <row r="103">
@@ -20645,7 +20645,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46110.85416666666</v>
+        <v>46110.75</v>
       </c>
     </row>
     <row r="104">
@@ -20842,27 +20842,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,133 +20895,133 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM104" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN104" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO104" t="n">
         <v>0</v>
       </c>
       <c r="AP104" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR104" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS104" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU104" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV104" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AW104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY104" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA104" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BB104" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC104" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD104" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF104" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46110.875</v>
+        <v>46110.8125</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="O105" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46110.875</v>
+        <v>46110.83333333334</v>
       </c>
     </row>
     <row r="106">
@@ -21236,27 +21236,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46110.875</v>
+        <v>46110.85416666666</v>
       </c>
     </row>
     <row r="107">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21482,145 +21482,736 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" t="n">
+        <v>0</v>
+      </c>
+      <c r="V107" t="n">
+        <v>0</v>
+      </c>
+      <c r="W107" t="n">
+        <v>0</v>
+      </c>
+      <c r="X107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH107" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI107" s="3" t="n">
+        <v>46110.875</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI108" s="3" t="n">
+        <v>46110.875</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>JS Kabylie</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ben Aknoun</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="P107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="n">
-        <v>0</v>
-      </c>
-      <c r="T107" t="n">
-        <v>0</v>
-      </c>
-      <c r="U107" t="n">
-        <v>0</v>
-      </c>
-      <c r="V107" t="n">
-        <v>0</v>
-      </c>
-      <c r="W107" t="n">
-        <v>0</v>
-      </c>
-      <c r="X107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH107" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI107" s="3" t="n">
+      <c r="P109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0</v>
+      </c>
+      <c r="S109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
+        <v>0</v>
+      </c>
+      <c r="U109" t="n">
+        <v>0</v>
+      </c>
+      <c r="V109" t="n">
+        <v>0</v>
+      </c>
+      <c r="W109" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH109" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI109" s="3" t="n">
+        <v>46110.875</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Algeria Ligue 1</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>MC Alger</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>USM Alger</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>suspended</t>
+        </is>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0</v>
+      </c>
+      <c r="S110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
+        <v>0</v>
+      </c>
+      <c r="U110" t="n">
+        <v>0</v>
+      </c>
+      <c r="V110" t="n">
+        <v>0</v>
+      </c>
+      <c r="W110" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI110" s="3" t="n">
         <v>46110.875</v>
       </c>
     </row>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>4.47</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.47</v>
+        <v>6.81</v>
       </c>
       <c r="S47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R48" t="n">
-        <v>6.81</v>
+        <v>2.47</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,16 +9977,16 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.93</v>
+        <v>3.92</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,112 +12621,112 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ62" t="n">
         <v>0</v>
@@ -12735,25 +12735,25 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
         <v>46110.5</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,133 +16167,133 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV80" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16797,10 +16797,10 @@
         <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17936,17 +17936,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.76</v>
+        <v>4.69</v>
       </c>
       <c r="R90" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="R91" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R93" t="n">
-        <v>2.73</v>
+        <v>3.44</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="R94" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R96" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22073,7 +22073,7 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P110" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="R25" t="n">
-        <v>4.47</v>
+        <v>16.5</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,79 +9863,79 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.47</v>
+        <v>6.81</v>
       </c>
       <c r="S48" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
@@ -9977,16 +9977,16 @@
         <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.92</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>1.81</v>
+        <v>4.88</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17739,17 +17739,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18330,17 +18330,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.64</v>
+        <v>2.31</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.74</v>
+        <v>2.67</v>
       </c>
       <c r="R92" t="n">
-        <v>2.73</v>
+        <v>3.42</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.24</v>
+        <v>2.47</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R93" t="n">
-        <v>3.44</v>
+        <v>2.99</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.31</v>
+        <v>2.64</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.67</v>
+        <v>2.74</v>
       </c>
       <c r="R94" t="n">
-        <v>3.42</v>
+        <v>2.73</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>4.47</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.41</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5383,10 +5383,10 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,16 +8401,16 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,17 +11238,17 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP56" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS56" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV56" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY56" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG56" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH56" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>4.88</v>
+        <v>3.6</v>
       </c>
       <c r="S57" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,133 +16167,133 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17542,17 +17542,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.76</v>
+        <v>4.69</v>
       </c>
       <c r="R88" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="R90" t="n">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18330,17 +18330,17 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="R92" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R93" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.74</v>
+        <v>5.25</v>
       </c>
       <c r="R94" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R95" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R96" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R97" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>4.47</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>8.4</v>
       </c>
       <c r="R26" t="n">
-        <v>4.47</v>
+        <v>16.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,79 +8287,79 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
@@ -8401,16 +8401,16 @@
         <v>0</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC40" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,112 +11439,112 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R56" t="n">
-        <v>4.88</v>
+        <v>3.6</v>
       </c>
       <c r="S56" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T56" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U56" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X56" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG56" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ56" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL56" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP56" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS56" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT56" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU56" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV56" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX56" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY56" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ56" t="n">
         <v>0</v>
@@ -11553,25 +11553,25 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC56" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE56" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF56" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG56" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
         <v>46110.5</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,112 +12621,112 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY62" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ62" t="n">
         <v>0</v>
@@ -12735,25 +12735,25 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG62" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI62" s="3" t="n">
         <v>46110.5</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17542,17 +17542,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17739,17 +17739,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17936,17 +17936,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>2.64</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R90" t="n">
-        <v>3.44</v>
+        <v>2.73</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="R91" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.47</v>
+        <v>1.56</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.78</v>
+        <v>4.69</v>
       </c>
       <c r="R92" t="n">
-        <v>2.99</v>
+        <v>5.4</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.74</v>
+        <v>5.25</v>
       </c>
       <c r="R93" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18921,17 +18921,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R95" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R97" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="R36" t="n">
-        <v>4.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.81</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD47" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,133 +16167,133 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV80" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,137 +16360,137 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17739,17 +17739,17 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.47</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.78</v>
+        <v>4.69</v>
       </c>
       <c r="R89" t="n">
-        <v>2.99</v>
+        <v>5.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R90" t="n">
-        <v>2.73</v>
+        <v>3.44</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R91" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.69</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>8.550000000000001</v>
+        <v>2.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>5.25</v>
+        <v>2.74</v>
       </c>
       <c r="R93" t="n">
-        <v>1.26</v>
+        <v>2.73</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R96" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G102" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5186,10 +5186,10 @@
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="R36" t="n">
-        <v>9.300000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="R38" t="n">
-        <v>4.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,16 +9189,16 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT57" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY57" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH57" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,112 +12621,112 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL62" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN62" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT62" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV62" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ62" t="n">
         <v>0</v>
@@ -12735,25 +12735,25 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC62" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH62" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
         <v>46110.5</v>
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,137 +16163,137 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16360,137 +16360,137 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17542,17 +17542,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="R88" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R90" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>8.550000000000001</v>
+        <v>2.47</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.25</v>
+        <v>2.78</v>
       </c>
       <c r="R91" t="n">
-        <v>1.26</v>
+        <v>2.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18921,17 +18921,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R95" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R96" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G110" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI110"/>
+  <dimension ref="A1:BI107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,112 +7499,112 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>4.34</v>
+        <v>4.88</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ36" t="n">
         <v>0</v>
@@ -7613,25 +7613,25 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI36" s="3" t="n">
         <v>46110.41666666666</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>9.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.73</v>
+        <v>3.95</v>
       </c>
       <c r="R39" t="n">
-        <v>2.48</v>
+        <v>4.34</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46110.4375</v>
+        <v>46110.41666666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46110.45833333334</v>
+        <v>46110.4375</v>
       </c>
     </row>
     <row r="41">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R45" t="n">
-        <v>6.81</v>
+        <v>2.47</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R49" t="n">
-        <v>3</v>
+        <v>6.81</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46110.46875</v>
+        <v>46110.45833333334</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46110.47916666666</v>
+        <v>46110.46875</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46110.48958333334</v>
+        <v>46110.47916666666</v>
       </c>
     </row>
     <row r="52">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P55" t="n">
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46110.5</v>
+        <v>46110.48958333334</v>
       </c>
     </row>
     <row r="56">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,112 +11636,112 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T57" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U57" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK57" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL57" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN57" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS57" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT57" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV57" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW57" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX57" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY57" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ57" t="n">
         <v>0</v>
@@ -11750,25 +11750,25 @@
         <v>0</v>
       </c>
       <c r="BB57" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC57" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD57" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE57" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF57" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH57" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
         <v>46110.5</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.93</v>
+        <v>3.92</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R60" t="n">
-        <v>3.6</v>
+        <v>1.81</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.92</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>3.08</v>
       </c>
       <c r="R61" t="n">
-        <v>1.81</v>
+        <v>2.93</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.84</v>
+        <v>3.72</v>
       </c>
       <c r="R63" t="n">
-        <v>6.71</v>
+        <v>6.08</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.31</v>
+        <v>1.61</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.08</v>
+        <v>3.68</v>
       </c>
       <c r="R64" t="n">
-        <v>2.93</v>
+        <v>4.87</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>4.87</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,137 +16163,137 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U80" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V80" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W80" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X80" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH80" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI80" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ80" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR80" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS80" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT80" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV80" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB80" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC80" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE80" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF80" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16508,27 +16508,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16557,137 +16557,137 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46110.625</v>
+        <v>46110.58333333334</v>
       </c>
     </row>
     <row r="83">
@@ -16705,27 +16705,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46110.64583333334</v>
+        <v>46110.625</v>
       </c>
     </row>
     <row r="84">
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46110.66666666666</v>
+        <v>46110.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.31</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.67</v>
+        <v>5.25</v>
       </c>
       <c r="R88" t="n">
-        <v>3.42</v>
+        <v>1.26</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>2.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.69</v>
+        <v>2.76</v>
       </c>
       <c r="R89" t="n">
-        <v>5.4</v>
+        <v>3.44</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>8.550000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.25</v>
+        <v>4.69</v>
       </c>
       <c r="R90" t="n">
-        <v>1.26</v>
+        <v>5.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R91" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="R94" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R95" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R96" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,597 +21621,6 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46110.875</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Paradou AC</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>CR Belouizdad</t>
-        </is>
-      </c>
-      <c r="G108" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N108" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O108" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY108" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH108" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI108" s="3" t="n">
-        <v>46110.875</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Algeria Ligue 1</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>JS Kabylie</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Ben Aknoun</t>
-        </is>
-      </c>
-      <c r="G109" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N109" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O109" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
-      <c r="R109" t="n">
-        <v>0</v>
-      </c>
-      <c r="S109" t="n">
-        <v>0</v>
-      </c>
-      <c r="T109" t="n">
-        <v>0</v>
-      </c>
-      <c r="U109" t="n">
-        <v>0</v>
-      </c>
-      <c r="V109" t="n">
-        <v>0</v>
-      </c>
-      <c r="W109" t="n">
-        <v>0</v>
-      </c>
-      <c r="X109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y109" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY109" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH109" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI109" s="3" t="n">
-        <v>46110.875</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="n">
-        <v>46110</v>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Jamaica Jamaica National Premier League</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Waterhouse</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Spanish Town Police FC</t>
-        </is>
-      </c>
-      <c r="G110" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N110" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0</v>
-      </c>
-      <c r="S110" t="n">
-        <v>0</v>
-      </c>
-      <c r="T110" t="n">
-        <v>0</v>
-      </c>
-      <c r="U110" t="n">
-        <v>0</v>
-      </c>
-      <c r="V110" t="n">
-        <v>0</v>
-      </c>
-      <c r="W110" t="n">
-        <v>0</v>
-      </c>
-      <c r="X110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y110" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY110" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH110" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI110" s="3" t="n">
         <v>46110.875</v>
       </c>
     </row>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI107"/>
+  <dimension ref="A1:BI108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46110.39583333334</v>
+        <v>46110.375</v>
       </c>
     </row>
     <row r="30">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,112 +7499,112 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4.88</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ36" t="n">
         <v>0</v>
@@ -7613,28 +7613,28 @@
         <v>0</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD36" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46110.41666666666</v>
+        <v>46110.39583333334</v>
       </c>
     </row>
     <row r="37">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="R37" t="n">
-        <v>9.300000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,112 +7893,112 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ38" t="n">
         <v>0</v>
@@ -8007,25 +8007,25 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46110.41666666666</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>FK Chernomorets Novorossiysk</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3.61</v>
+        <v>1.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.73</v>
+        <v>6.2</v>
       </c>
       <c r="R40" t="n">
-        <v>2.48</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46110.4375</v>
+        <v>46110.41666666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>FK Chernomorets Novorossiysk</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46110.45833333334</v>
+        <v>46110.4375</v>
       </c>
     </row>
     <row r="42">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>6.81</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46110.46875</v>
+        <v>46110.45833333334</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46110.47916666666</v>
+        <v>46110.46875</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46110.48958333334</v>
+        <v>46110.47916666666</v>
       </c>
     </row>
     <row r="53">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46110.5</v>
+        <v>46110.48958333334</v>
       </c>
     </row>
     <row r="57">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>6.71</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.31</v>
+        <v>3.92</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>2.93</v>
+        <v>1.81</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="R62" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.72</v>
+        <v>3.25</v>
       </c>
       <c r="R63" t="n">
-        <v>6.08</v>
+        <v>3.6</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.68</v>
+        <v>3.72</v>
       </c>
       <c r="R64" t="n">
-        <v>4.87</v>
+        <v>6.08</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46110.52083333334</v>
+        <v>46110.5</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46110.54166666666</v>
+        <v>46110.52083333334</v>
       </c>
     </row>
     <row r="74">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.93</v>
+        <v>2.99</v>
       </c>
       <c r="R74" t="n">
-        <v>2.58</v>
+        <v>3.09</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46110.5625</v>
+        <v>46110.54166666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16163,17 +16163,17 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46110.58333333334</v>
+        <v>46110.5625</v>
       </c>
     </row>
     <row r="81">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16705,27 +16705,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>New England II</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16754,7 +16754,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46110.625</v>
+        <v>46110.58333333334</v>
       </c>
     </row>
     <row r="84">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>New England II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -16994,10 +16994,10 @@
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46110.64583333334</v>
+        <v>46110.625</v>
       </c>
     </row>
     <row r="85">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46110.66666666666</v>
+        <v>46110.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.69</v>
+        <v>5.25</v>
       </c>
       <c r="R90" t="n">
-        <v>5.4</v>
+        <v>1.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.74</v>
+        <v>4.69</v>
       </c>
       <c r="R91" t="n">
-        <v>2.73</v>
+        <v>5.4</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18527,17 +18527,17 @@
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19069,7 +19069,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>3.13</v>
+        <v>2.31</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="R95" t="n">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46110.70833333334</v>
+        <v>46110.66666666666</v>
       </c>
     </row>
     <row r="96">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R97" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19660,27 +19660,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46110.72916666666</v>
+        <v>46110.70833333334</v>
       </c>
     </row>
     <row r="99">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46110.75</v>
+        <v>46110.72916666666</v>
       </c>
     </row>
     <row r="104">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,133 +20895,133 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="T104" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="U104" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V104" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W104" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="X104" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB104" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ104" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM104" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN104" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AO104" t="n">
         <v>0</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS104" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT104" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AU104" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AV104" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="AW104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AX104" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AY104" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BA104" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="BB104" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC104" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="BD104" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="BF104" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BG104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46110.8125</v>
+        <v>46110.75</v>
       </c>
     </row>
     <row r="105">
@@ -21039,12 +21039,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Gotham FC</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,133 +21092,133 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL105" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM105" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN105" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AO105" t="n">
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS105" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AU105" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AV105" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AW105" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX105" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AY105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA105" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="BB105" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC105" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BD105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF105" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46110.83333333334</v>
+        <v>46110.8125</v>
       </c>
     </row>
     <row r="106">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Gotham FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46110.85416666666</v>
+        <v>46110.83333333334</v>
       </c>
     </row>
     <row r="107">
@@ -21433,27 +21433,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,6 +21621,203 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
+        <v>46110.85416666666</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Jamaica Jamaica National Premier League</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Waterhouse</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Spanish Town Police FC</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH108" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI108" s="3" t="n">
         <v>46110.875</v>
       </c>
     </row>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="R2" t="n">
-        <v>3.24</v>
+        <v>4.62</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>3.54</v>
       </c>
       <c r="R3" t="n">
-        <v>4.62</v>
+        <v>3.24</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>4.47</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="R27" t="n">
-        <v>2.41</v>
+        <v>1.84</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="S28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>3.35</v>
+        <v>2.41</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="R37" t="n">
-        <v>4.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="R40" t="n">
-        <v>9.300000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.92</v>
+        <v>1.61</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>3.68</v>
       </c>
       <c r="R61" t="n">
-        <v>1.81</v>
+        <v>4.87</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF61" t="n">
         <v>1.98</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>1.83</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="R62" t="n">
-        <v>2.93</v>
+        <v>6.08</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.93</v>
+        <v>2.31</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="R63" t="n">
-        <v>3.6</v>
+        <v>2.93</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>6.08</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>1.61</v>
+        <v>3.92</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="R65" t="n">
-        <v>4.87</v>
+        <v>1.81</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF65" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AF65" t="n">
-        <v>1.98</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.62</v>
+        <v>2.1</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="R75" t="n">
-        <v>2.58</v>
+        <v>3.27</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="R78" t="n">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R89" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH89" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18133,17 +18133,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.56</v>
+        <v>2.47</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.69</v>
+        <v>2.78</v>
       </c>
       <c r="R91" t="n">
-        <v>5.4</v>
+        <v>2.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.47</v>
+        <v>2.31</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="R94" t="n">
-        <v>2.99</v>
+        <v>3.42</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="R95" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G102" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH2" t="n">
         <v>1.58</v>
       </c>
-      <c r="Q2" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="R2" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.54</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>3.24</v>
+        <v>4.62</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cheongju</t>
+          <t>Suwon</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Busan I'Park</t>
+          <t>Paju Citizen</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL4" t="n">
         <v>2.05</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suwon</t>
+          <t>Cheongju</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Paju Citizen</t>
+          <t>Busan I'Park</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>3.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>4.47</v>
+        <v>2.05</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>2.05</v>
+        <v>4.47</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5580,10 +5580,10 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.95</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R28" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brito</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,112 +7696,112 @@
         </is>
       </c>
       <c r="P37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R37" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U37" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH37" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ37" t="n">
         <v>0</v>
@@ -7810,25 +7810,25 @@
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BH37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BI37" s="3" t="n">
         <v>46110.41666666666</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brito</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,112 +7893,112 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="R38" t="n">
-        <v>4.88</v>
+        <v>4.34</v>
       </c>
       <c r="S38" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS38" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
         <v>0</v>
@@ -8007,25 +8007,25 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC38" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD38" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BH38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
         <v>46110.41666666666</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="R40" t="n">
-        <v>4.34</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Os Marialvas</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>UD da Serra</t>
+          <t>Marinhense</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Fátima</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Marinhense</t>
+          <t>Oliveira Hospital</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Os Marialvas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>UD da Serra</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Samora Correir</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Peniche</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Amarante</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.8</v>
+        <v>1.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>2.47</v>
+        <v>6.81</v>
       </c>
       <c r="S46" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,16 +9583,16 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Samora Correir</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Peniche</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fátima</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oliveira Hospital</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Amarante</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,79 +10257,79 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.67</v>
+        <v>2.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="R50" t="n">
-        <v>6.81</v>
+        <v>2.47</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,16 +10371,16 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.84</v>
+        <v>3.4</v>
       </c>
       <c r="R59" t="n">
-        <v>6.71</v>
+        <v>5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.61</v>
+        <v>2.31</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.68</v>
+        <v>3.08</v>
       </c>
       <c r="R61" t="n">
-        <v>4.87</v>
+        <v>2.93</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>FC Alverca II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.72</v>
+        <v>3.34</v>
       </c>
       <c r="R62" t="n">
-        <v>6.08</v>
+        <v>3.69</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.31</v>
+        <v>1.5</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="R63" t="n">
-        <v>2.93</v>
+        <v>6.08</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>6.71</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FC Alverca II</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,17 +13405,17 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.1</v>
+        <v>2.57</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="R75" t="n">
-        <v>3.27</v>
+        <v>3.09</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T82" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U82" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA82" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB82" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF82" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI82" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM82" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN82" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR82" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV82" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX82" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB82" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC82" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV83" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW83" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY83" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA83" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB83" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE83" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17191,10 +17191,10 @@
         <v>0</v>
       </c>
       <c r="AC85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE85" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18133,17 +18133,17 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.47</v>
+        <v>1.56</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.78</v>
+        <v>4.69</v>
       </c>
       <c r="R91" t="n">
-        <v>2.99</v>
+        <v>5.4</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R92" t="n">
-        <v>2.73</v>
+        <v>3.44</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.69</v>
+        <v>2.74</v>
       </c>
       <c r="R93" t="n">
-        <v>5.4</v>
+        <v>2.73</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18921,17 +18921,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.76</v>
+        <v>2.67</v>
       </c>
       <c r="R95" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R96" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G102" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="X2" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="BC2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="U3" t="n">
-        <v>4.8</v>
+        <v>3.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BE3" t="n">
         <v>2.02</v>
       </c>
-      <c r="AH3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2583,70 +2583,70 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>4.89</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2780,70 +2780,70 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Real Sociedad W</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Logroño W</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.1</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.3</v>
+        <v>3.2</v>
       </c>
       <c r="R13" t="n">
-        <v>15.5</v>
+        <v>3.75</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Sociedad W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Logroño W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3568,70 +3568,70 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4989,10 +4989,10 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.41</v>
+        <v>1.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>8.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.05</v>
+        <v>16.5</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,13 +5219,13 @@
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU24" t="n">
         <v>0</v>
@@ -5234,34 +5234,34 @@
         <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5341,70 +5341,70 @@
         <v>4.47</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5538,70 +5538,70 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>3.48</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="R27" t="n">
-        <v>3.35</v>
+        <v>1.97</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>2.32</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="R28" t="n">
-        <v>1.84</v>
+        <v>3.05</v>
       </c>
       <c r="S28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="X28" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT28" t="n">
         <v>4.5</v>
       </c>
-      <c r="T28" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X28" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AF28" t="n">
+      <c r="AU28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AW28" t="n">
         <v>1.55</v>
       </c>
-      <c r="AG28" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.16</v>
+        <v>2.62</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -7705,22 +7705,22 @@
         <v>4.88</v>
       </c>
       <c r="S37" t="n">
-        <v>2.33</v>
+        <v>2.24</v>
       </c>
       <c r="T37" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="U37" t="n">
         <v>5.85</v>
       </c>
       <c r="V37" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W37" t="n">
         <v>2.53</v>
       </c>
       <c r="X37" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="Y37" t="n">
         <v>1.32</v>
@@ -7738,34 +7738,34 @@
         <v>1.32</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AE37" t="n">
         <v>2.05</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG37" t="n">
         <v>3.8</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM37" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.17</v>
       </c>
       <c r="AN37" t="n">
         <v>2.03</v>
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.61</v>
+        <v>2.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="R41" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.81</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9872,124 +9872,124 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10257,34 +10257,34 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R50" t="n">
-        <v>2.47</v>
+        <v>2.25</v>
       </c>
       <c r="S50" t="n">
-        <v>3.54</v>
+        <v>4.12</v>
       </c>
       <c r="T50" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="U50" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="V50" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="W50" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="X50" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z50" t="n">
         <v>8.5</v>
@@ -10296,40 +10296,40 @@
         <v>1.06</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AE50" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG50" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="AH50" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AI50" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ50" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK50" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AL50" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AN50" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10371,16 +10371,16 @@
         <v>0</v>
       </c>
       <c r="BB50" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BC50" t="n">
-        <v>2.29</v>
+        <v>2.36</v>
       </c>
       <c r="BD50" t="n">
-        <v>3.28</v>
+        <v>3.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="R51" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11842,70 +11842,70 @@
         <v>1.81</v>
       </c>
       <c r="S58" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG58" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI58" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL58" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM58" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN58" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO58" t="n">
         <v>0</v>
@@ -11947,19 +11947,19 @@
         <v>0</v>
       </c>
       <c r="BB58" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE58" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF58" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG58" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R67" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14403,70 +14403,70 @@
         <v>2.27</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI71" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK71" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM71" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN71" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
@@ -14508,19 +14508,19 @@
         <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC71" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE71" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF71" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15191,70 +15191,70 @@
         <v>3.09</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U75" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V75" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W75" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X75" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC75" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD75" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI75" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL75" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM75" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN75" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
@@ -15296,19 +15296,19 @@
         <v>0</v>
       </c>
       <c r="BB75" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC75" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD75" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE75" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF75" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16176,40 +16176,40 @@
         <v>2.53</v>
       </c>
       <c r="S80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W80" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X80" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE80" t="n">
         <v>1.81</v>
@@ -16218,82 +16218,82 @@
         <v>1.92</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI80" t="n">
-        <v>0</v>
+        <v>5.72</v>
       </c>
       <c r="AJ80" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK80" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM80" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN80" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO80" t="n">
         <v>0</v>
       </c>
       <c r="AP80" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AR80" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AW80" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX80" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY80" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BA80" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BB80" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC80" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE80" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF80" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,133 +16561,133 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U82" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V82" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W82" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB82" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC82" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF82" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL82" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO82" t="n">
         <v>0</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR82" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS82" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT82" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU82" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV82" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX82" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ82" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA82" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB82" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC82" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE82" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF82" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17782,10 +17782,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17936,17 +17936,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17991,10 +17991,10 @@
         <v>0</v>
       </c>
       <c r="AG89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.47</v>
+        <v>2.24</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="R90" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.56</v>
+        <v>2.47</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.69</v>
+        <v>2.78</v>
       </c>
       <c r="R91" t="n">
-        <v>5.4</v>
+        <v>2.99</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.24</v>
+        <v>1.56</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.76</v>
+        <v>4.69</v>
       </c>
       <c r="R92" t="n">
-        <v>3.44</v>
+        <v>5.4</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q93" t="n">
-        <v>2.74</v>
+        <v>5.25</v>
       </c>
       <c r="R93" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18921,17 +18921,17 @@
       </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="R96" t="n">
-        <v>3.48</v>
+        <v>3.02</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.13</v>
+        <v>2.22</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="R97" t="n">
-        <v>2.37</v>
+        <v>3.48</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.26</v>
+        <v>3.13</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3</v>
+        <v>2.79</v>
       </c>
       <c r="R98" t="n">
-        <v>3.02</v>
+        <v>2.37</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>6.25</v>
+        <v>4.02</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>4.02</v>
+        <v>6.25</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>2.35</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>1.39</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>3.75</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,79 +3559,79 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.1</v>
+        <v>2.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.09</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>7.17</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="R18" t="n">
-        <v>2.57</v>
+        <v>5.09</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.62</v>
+        <v>2.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.11</v>
+        <v>1.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>8.4</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>16.5</v>
+        <v>4.47</v>
       </c>
       <c r="S24" t="n">
-        <v>1.48</v>
+        <v>2.2</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>2.24</v>
       </c>
       <c r="U24" t="n">
-        <v>10</v>
+        <v>4.75</v>
       </c>
       <c r="V24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BF24" t="n">
         <v>1.2</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>1.38</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="T25" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="U25" t="n">
-        <v>4.75</v>
+        <v>3.28</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W25" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="X25" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC25" t="n">
         <v>1.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC25" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S26" t="n">
-        <v>3.08</v>
+        <v>1.48</v>
       </c>
       <c r="T26" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="U26" t="n">
-        <v>3.28</v>
+        <v>10</v>
       </c>
       <c r="V26" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W26" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="X26" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AB26" t="n">
         <v>1.01</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AI26" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="AJ26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AN26" t="n">
-        <v>1.43</v>
+        <v>5.5</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
@@ -5628,34 +5628,34 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="BD26" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Kristianstad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.48</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.97</v>
+        <v>2.41</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,133 +5923,133 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.32</v>
+        <v>3.48</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="R28" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="S28" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="U28" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="V28" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W28" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="X28" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI28" t="n">
         <v>9</v>
       </c>
-      <c r="AA28" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AJ28" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL28" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="BC28" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="BD28" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kristianstad</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>2.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="R29" t="n">
-        <v>2.41</v>
+        <v>3.05</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Uppsala W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Uppsala W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="R40" t="n">
-        <v>9.300000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Camacha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sokol Saratov</t>
+          <t>Bragança</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Camacha</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bragança</t>
+          <t>Sokol Saratov</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9872,124 +9872,124 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10069,124 +10069,124 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX49" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA49" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BB49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD49" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE49" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF49" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13405,7 +13405,7 @@
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CDA Navalcarnero</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,79 +14394,79 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="AJ71" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK71" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AL71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AM71" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN71" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AO71" t="n">
         <v>0</v>
@@ -14508,19 +14508,19 @@
         <v>0</v>
       </c>
       <c r="BB71" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC71" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BD71" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE71" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BF71" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>CDA Navalcarnero</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,79 +14591,79 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="T72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U72" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V72" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W72" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X72" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA72" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB72" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD72" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI72" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK72" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL72" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AM72" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN72" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO72" t="n">
         <v>0</v>
@@ -14705,19 +14705,19 @@
         <v>0</v>
       </c>
       <c r="BB72" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC72" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD72" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE72" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF72" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>3.27</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,79 +15182,79 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U75" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V75" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W75" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X75" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD75" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE75" t="n">
         <v>2.15</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG75" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ75" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL75" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM75" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN75" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO75" t="n">
         <v>0</v>
@@ -15296,19 +15296,19 @@
         <v>0</v>
       </c>
       <c r="BB75" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC75" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE75" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BF75" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,79 +15379,79 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE76" t="n">
         <v>2.15</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
@@ -15493,19 +15493,19 @@
         <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD76" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF76" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ81" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL81" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR81" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS81" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT81" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU81" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV81" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB81" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC81" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE81" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF81" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17782,10 +17782,10 @@
         <v>0</v>
       </c>
       <c r="AC88" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD88" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17936,17 +17936,17 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.76</v>
+        <v>5.25</v>
       </c>
       <c r="R90" t="n">
-        <v>3.44</v>
+        <v>1.26</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R91" t="n">
-        <v>2.99</v>
+        <v>2.73</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.56</v>
+        <v>2.31</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.69</v>
+        <v>2.67</v>
       </c>
       <c r="R92" t="n">
-        <v>5.4</v>
+        <v>3.42</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.64</v>
+        <v>2.24</v>
       </c>
       <c r="Q94" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R94" t="n">
-        <v>2.73</v>
+        <v>3.44</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.31</v>
+        <v>2.47</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
       <c r="R95" t="n">
-        <v>3.42</v>
+        <v>2.99</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R96" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R97" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R98" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G103" t="n">

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R2" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="S2" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="T2" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="U2" t="n">
-        <v>4.8</v>
+        <v>3.78</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="X2" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF2" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BE2" t="n">
         <v>2.02</v>
       </c>
-      <c r="AH2" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF2" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R3" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="T3" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="U3" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="X3" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH3" t="n">
+      <c r="BC3" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI3" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BD3" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>4.02</v>
+        <v>6.25</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R8" t="n">
-        <v>6.25</v>
+        <v>4.02</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>1.83</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.6</v>
+        <v>2.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>UD Poblense</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>Orihuela CF</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.35</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orihuela CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3371,124 +3371,124 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>2.03</v>
       </c>
       <c r="T15" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
-        <v>3.66</v>
+        <v>7.17</v>
       </c>
       <c r="V15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W15" t="n">
-        <v>2.91</v>
+        <v>2.53</v>
       </c>
       <c r="X15" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AI15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD15" t="n">
         <v>3.5</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BE15" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>1.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="R16" t="n">
-        <v>2.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3604,10 +3604,10 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.62</v>
+        <v>2.35</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5.09</v>
       </c>
       <c r="S17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.1</v>
+        <v>2.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.32</v>
+        <v>2.94</v>
       </c>
       <c r="R18" t="n">
-        <v>5.09</v>
+        <v>2.57</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rayo Cantabria</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Rayo Cantabria</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Tenerife W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Madrid CFF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.41</v>
+        <v>1.65</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>2.05</v>
+        <v>4.47</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tenerife W</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Madrid CFF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.2</v>
+        <v>3.08</v>
       </c>
       <c r="T24" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="U24" t="n">
-        <v>4.75</v>
+        <v>3.28</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="X24" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC24" t="n">
         <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5249,19 +5249,19 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="S25" t="n">
-        <v>3.08</v>
+        <v>1.48</v>
       </c>
       <c r="T25" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="U25" t="n">
-        <v>3.28</v>
+        <v>10</v>
       </c>
       <c r="V25" t="n">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="W25" t="n">
-        <v>2.74</v>
+        <v>3.8</v>
       </c>
       <c r="X25" t="n">
-        <v>2.66</v>
+        <v>1.95</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="Z25" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AB25" t="n">
         <v>1.01</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.97</v>
+        <v>1.92</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>1.76</v>
       </c>
       <c r="AI25" t="n">
-        <v>6</v>
+        <v>3.34</v>
       </c>
       <c r="AJ25" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AN25" t="n">
-        <v>1.43</v>
+        <v>5.5</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5416,13 +5416,13 @@
         <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU25" t="n">
         <v>0</v>
@@ -5431,34 +5431,34 @@
         <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.69</v>
+        <v>2.25</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.11</v>
+        <v>3.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>8.4</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>16.5</v>
+        <v>2.05</v>
       </c>
       <c r="S26" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5613,13 +5613,13 @@
         <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
         <v>0</v>
@@ -5628,34 +5628,34 @@
         <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Juventus II</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Juventus II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Brighton &amp; Hove Albion Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9872,124 +9872,124 @@
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL48" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO48" t="n">
         <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AR48" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS48" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT48" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AV48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW48" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX48" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY48" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA48" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BB48" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD48" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF48" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10069,124 +10069,124 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AO49" t="n">
         <v>0</v>
       </c>
       <c r="AP49" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AR49" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AU49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AV49" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AW49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX49" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA49" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="BB49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BC49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE49" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF49" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BG49" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AZ W</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Utrecht W</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>AZ W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Utrecht W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Deportivo Alaves II</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="R57" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves II</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.62</v>
+        <v>3.75</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R59" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Alcoyano</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,79 +14985,79 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.4</v>
+        <v>2.57</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.7</v>
+        <v>2.99</v>
       </c>
       <c r="R74" t="n">
-        <v>8.699999999999999</v>
+        <v>3.09</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="V74" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W74" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X74" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA74" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC74" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD74" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE74" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI74" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK74" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL74" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AM74" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN74" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO74" t="n">
         <v>0</v>
@@ -15099,19 +15099,19 @@
         <v>0</v>
       </c>
       <c r="BB74" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC74" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD74" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE74" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BF74" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,79 +15379,79 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
         <v>2.15</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AG76" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
@@ -15493,19 +15493,19 @@
         <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="BC76" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="BE76" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Alcoyano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.93</v>
+        <v>3.7</v>
       </c>
       <c r="R77" t="n">
-        <v>2.58</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Yacoub El Mansour</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Olympic Safi</t>
+          <t>Paços de Ferreira</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,133 +16364,133 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AO81" t="n">
         <v>0</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wydad Casablanca</t>
+          <t>Yacoub El Mansour</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympic Safi</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Wydad Casablanca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Paços de Ferreira</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U83" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="V83" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB83" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC83" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AM83" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN83" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AR83" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AS83" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT83" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV83" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW83" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AX83" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AY83" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BA83" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BB83" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC83" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD83" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE83" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF83" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17388,10 +17388,10 @@
         <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17585,10 +17585,10 @@
         <v>0</v>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE87" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q89" t="n">
-        <v>4.69</v>
+        <v>2.74</v>
       </c>
       <c r="R89" t="n">
-        <v>5.4</v>
+        <v>2.73</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>8.550000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.25</v>
+        <v>4.69</v>
       </c>
       <c r="R90" t="n">
-        <v>1.26</v>
+        <v>5.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.74</v>
+        <v>5.25</v>
       </c>
       <c r="R91" t="n">
-        <v>2.73</v>
+        <v>1.26</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Maghreb Fès</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18724,17 +18724,17 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Maghreb Fès</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19118,17 +19118,17 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.22</v>
+        <v>3.13</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="R96" t="n">
-        <v>3.48</v>
+        <v>2.37</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Lexington</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>3.13</v>
+        <v>2.26</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.79</v>
+        <v>3.3</v>
       </c>
       <c r="R97" t="n">
-        <v>2.37</v>
+        <v>3.02</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>San Antonio</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lexington</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.3</v>
+        <v>2.77</v>
       </c>
       <c r="R98" t="n">
-        <v>3.02</v>
+        <v>3.48</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>

--- a/jogos_2026-03-29.xlsx
+++ b/jogos_2026-03-29.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>SD Raiders</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -801,133 +801,133 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>4.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="T2" t="n">
-        <v>2.27</v>
+        <v>2.38</v>
       </c>
       <c r="U2" t="n">
-        <v>3.78</v>
+        <v>4.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>3.34</v>
+        <v>3.58</v>
       </c>
       <c r="X2" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.75</v>
+        <v>4.45</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
       </c>
       <c r="AC2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
         <v>1.11</v>
       </c>
-      <c r="AD2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="BC2" t="n">
         <v>1.58</v>
       </c>
-      <c r="AI2" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>1.69</v>
-      </c>
       <c r="BD2" t="n">
-        <v>5.05</v>
+        <v>5.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SD Raiders</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.98</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>4.62</v>
+        <v>3.1</v>
       </c>
       <c r="S3" t="n">
-        <v>2.16</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="U3" t="n">
-        <v>4.8</v>
+        <v>3.78</v>
       </c>
       <c r="V3" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="W3" t="n">
-        <v>3.58</v>
+        <v>3.34</v>
       </c>
       <c r="X3" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AB3" t="n">
         <v>1</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AD3" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AF3" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AG3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BE3" t="n">
         <v>2.02</v>
       </c>
-      <c r="AH3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2.15</v>
-      </c>
       <c r="BF3" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Basconia</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1.42</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>6.25</v>
+        <v>4.02</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1831,10 +1831,10 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Basconia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.42</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>4.02</v>
+        <v>6.25</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2028,10 +2028,10 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.6</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>UD Poblense</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>2.9</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="S11" t="n">
-        <v>4.89</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>5.09</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
  